--- a/demo-data/olivine_demo_vansales.xlsx
+++ b/demo-data/olivine_demo_vansales.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.4</v>
+        <v>13.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -533,22 +533,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1562.12</v>
+        <v>1270.72</v>
       </c>
       <c r="H2" t="n">
-        <v>390.53</v>
+        <v>317.68</v>
       </c>
       <c r="I2" t="n">
-        <v>390.53</v>
+        <v>317.68</v>
       </c>
       <c r="J2" t="n">
-        <v>390.53</v>
+        <v>317.68</v>
       </c>
       <c r="K2" t="n">
-        <v>390.53</v>
+        <v>317.68</v>
       </c>
       <c r="L2" t="n">
-        <v>1562.12</v>
+        <v>1270.72</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1631.04</v>
+        <v>1138.32</v>
       </c>
       <c r="H3" t="n">
-        <v>407.76</v>
+        <v>284.58</v>
       </c>
       <c r="I3" t="n">
-        <v>407.76</v>
+        <v>284.58</v>
       </c>
       <c r="J3" t="n">
-        <v>407.76</v>
+        <v>284.58</v>
       </c>
       <c r="K3" t="n">
-        <v>407.76</v>
+        <v>284.58</v>
       </c>
       <c r="L3" t="n">
-        <v>1631.04</v>
+        <v>1138.32</v>
       </c>
     </row>
     <row r="4">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -629,22 +629,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1273.24</v>
+        <v>1336.28</v>
       </c>
       <c r="H4" t="n">
-        <v>318.31</v>
+        <v>334.07</v>
       </c>
       <c r="I4" t="n">
-        <v>318.31</v>
+        <v>334.07</v>
       </c>
       <c r="J4" t="n">
-        <v>318.31</v>
+        <v>334.07</v>
       </c>
       <c r="K4" t="n">
-        <v>318.31</v>
+        <v>334.07</v>
       </c>
       <c r="L4" t="n">
-        <v>1273.24</v>
+        <v>1336.28</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.5</v>
+        <v>7.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -677,22 +677,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1429.52</v>
+        <v>1551.96</v>
       </c>
       <c r="H5" t="n">
-        <v>357.38</v>
+        <v>387.99</v>
       </c>
       <c r="I5" t="n">
-        <v>357.38</v>
+        <v>387.99</v>
       </c>
       <c r="J5" t="n">
-        <v>357.38</v>
+        <v>387.99</v>
       </c>
       <c r="K5" t="n">
-        <v>357.38</v>
+        <v>387.99</v>
       </c>
       <c r="L5" t="n">
-        <v>1429.52</v>
+        <v>1551.96</v>
       </c>
     </row>
     <row r="6">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1149.04</v>
+        <v>1592.16</v>
       </c>
       <c r="H6" t="n">
-        <v>287.26</v>
+        <v>398.04</v>
       </c>
       <c r="I6" t="n">
-        <v>287.26</v>
+        <v>398.04</v>
       </c>
       <c r="J6" t="n">
-        <v>287.26</v>
+        <v>398.04</v>
       </c>
       <c r="K6" t="n">
-        <v>287.26</v>
+        <v>398.04</v>
       </c>
       <c r="L6" t="n">
-        <v>1149.04</v>
+        <v>1592.16</v>
       </c>
     </row>
     <row r="7">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1273.76</v>
+        <v>1096.56</v>
       </c>
       <c r="H7" t="n">
-        <v>318.44</v>
+        <v>274.14</v>
       </c>
       <c r="I7" t="n">
-        <v>318.44</v>
+        <v>274.14</v>
       </c>
       <c r="J7" t="n">
-        <v>318.44</v>
+        <v>274.14</v>
       </c>
       <c r="K7" t="n">
-        <v>318.44</v>
+        <v>274.14</v>
       </c>
       <c r="L7" t="n">
-        <v>1273.76</v>
+        <v>1096.56</v>
       </c>
     </row>
     <row r="8">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -821,22 +821,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1477.88</v>
+        <v>1476.12</v>
       </c>
       <c r="H8" t="n">
-        <v>369.47</v>
+        <v>369.03</v>
       </c>
       <c r="I8" t="n">
-        <v>369.47</v>
+        <v>369.03</v>
       </c>
       <c r="J8" t="n">
-        <v>369.47</v>
+        <v>369.03</v>
       </c>
       <c r="K8" t="n">
-        <v>369.47</v>
+        <v>369.03</v>
       </c>
       <c r="L8" t="n">
-        <v>1477.88</v>
+        <v>1476.12</v>
       </c>
     </row>
     <row r="9">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.9</v>
+        <v>7.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -869,22 +869,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1101.64</v>
+        <v>1271.96</v>
       </c>
       <c r="H9" t="n">
-        <v>275.41</v>
+        <v>317.99</v>
       </c>
       <c r="I9" t="n">
-        <v>275.41</v>
+        <v>317.99</v>
       </c>
       <c r="J9" t="n">
-        <v>275.41</v>
+        <v>317.99</v>
       </c>
       <c r="K9" t="n">
-        <v>275.41</v>
+        <v>317.99</v>
       </c>
       <c r="L9" t="n">
-        <v>1101.64</v>
+        <v>1271.96</v>
       </c>
     </row>
     <row r="10">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1326.36</v>
+        <v>1293.48</v>
       </c>
       <c r="H10" t="n">
-        <v>331.59</v>
+        <v>323.37</v>
       </c>
       <c r="I10" t="n">
-        <v>331.59</v>
+        <v>323.37</v>
       </c>
       <c r="J10" t="n">
-        <v>331.59</v>
+        <v>323.37</v>
       </c>
       <c r="K10" t="n">
-        <v>331.59</v>
+        <v>323.37</v>
       </c>
       <c r="L10" t="n">
-        <v>1326.36</v>
+        <v>1293.48</v>
       </c>
     </row>
     <row r="11">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.9</v>
+        <v>5.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -965,22 +965,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1369.04</v>
+        <v>1005.8</v>
       </c>
       <c r="H11" t="n">
-        <v>342.26</v>
+        <v>251.45</v>
       </c>
       <c r="I11" t="n">
-        <v>342.26</v>
+        <v>251.45</v>
       </c>
       <c r="J11" t="n">
-        <v>342.26</v>
+        <v>251.45</v>
       </c>
       <c r="K11" t="n">
-        <v>342.26</v>
+        <v>251.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1369.04</v>
+        <v>1005.8</v>
       </c>
     </row>
   </sheetData>
